--- a/Results/phylo_signal_random_summary.xlsx
+++ b/Results/phylo_signal_random_summary.xlsx
@@ -1,62 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\OneDrive\Desktop\Artigos_coauthor\Iberian_plants\Extinction_dynamics_Iberic\Results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E67AEC2-C4EF-4C37-AB48-15B1ED8852CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
-  <si>
-    <t>Peninsular Spain</t>
-  </si>
-  <si>
-    <t>Eastern Andalusia</t>
-  </si>
-  <si>
-    <t>&lt; 0.001</t>
-  </si>
-  <si>
-    <t>Mean Estimate</t>
-  </si>
-  <si>
-    <t>SD estimate</t>
-  </si>
-  <si>
-    <t>p-value (mean)</t>
-  </si>
-  <si>
-    <t>Blomberg's K</t>
-  </si>
-  <si>
-    <t>Pagel's λ</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,19 +30,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,24 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -132,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -184,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -218,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -253,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -429,101 +350,122 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>p_value_mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.85828197337193624</v>
-      </c>
-      <c r="D2" s="5">
-        <v>3.2892887409276379E-2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>2</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lambda</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.00696397694435901</v>
+      </c>
+      <c r="C2">
+        <v>0.01979560016962631</v>
+      </c>
+      <c r="D2">
+        <v>0.9702245334100381</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Peninsula</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5">
-        <v>3.4811334776825492E-2</v>
-      </c>
-      <c r="D3" s="5">
-        <v>2.5629995634163E-3</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2.53E-2</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.02655115760282746</v>
+      </c>
+      <c r="C3">
+        <v>0.001777363918207558</v>
+      </c>
+      <c r="D3">
+        <v>0.0633</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Peninsula</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5">
-        <v>7.3313743585740569E-5</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lambda</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.3714397252717034</v>
+      </c>
+      <c r="C4">
+        <v>0.04864477994129402</v>
+      </c>
+      <c r="D4">
+        <v>0.0005199372651334285</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Andalusia</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1.277077278499838E-2</v>
-      </c>
-      <c r="D5" s="5">
-        <v>4.7176614861888351E-4</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.50650000000000028</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.04003471635619249</v>
+      </c>
+      <c r="C5">
+        <v>0.003377935250190388</v>
+      </c>
+      <c r="D5">
+        <v>0.01</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Andalusia</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>